--- a/data/metadata_raw/active_enterprises.xlsx
+++ b/data/metadata_raw/active_enterprises.xlsx
@@ -3629,7 +3629,7 @@
     <t>2022-06-23</t>
   </si>
   <si>
-    <t>2024-07-25</t>
+    <t>2026-01-09</t>
   </si>
   <si>
     <t>1.09.01.0023</t>
